--- a/data-manipulation-scripts/sheets-cleanup/sheets/ROLDANAS - 18_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ROLDANAS - 18_01.xlsx
@@ -76,19 +76,19 @@
     <t>7908073714431</t>
   </si>
   <si>
-    <t>CARCAÇA ACELERADOR SMARTFOX FAN150-160/ TITAN150 2014 TITAN160</t>
+    <t>ROLDANA ACELERADOR SMARTFOX FAN150-160/ TITAN150 2014 TITAN160</t>
   </si>
   <si>
     <t>7908073723914</t>
   </si>
   <si>
-    <t>CARCAÇA ACELERADOR SMARTFOX BIZ125-110I 2018 POP110I</t>
+    <t>ROLDANA ACELERADOR SMARTFOX BIZ125-110I 2018 POP110I</t>
   </si>
   <si>
     <t>7899468067808</t>
   </si>
   <si>
-    <t>CARCAÇA ACELERADOR TRILHA FAN TIITAN150 2014 A 2015/ TITAN FAN160 2016</t>
+    <t>ROLDANA ACELERADOR TRILHA FAN TIITAN150 2014 A 2015/ TITAN FAN160 2016</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -399,7 +399,9 @@
       <c r="C2" s="4">
         <v>10.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
@@ -411,7 +413,9 @@
       <c r="C3" s="4">
         <v>7.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
@@ -423,7 +427,9 @@
       <c r="C4" s="4">
         <v>8.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="4">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
@@ -435,7 +441,9 @@
       <c r="C5" s="4">
         <v>2.0</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5" s="4">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
@@ -447,7 +455,9 @@
       <c r="C6" s="4">
         <v>6.0</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6" s="4">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
@@ -459,7 +469,9 @@
       <c r="C7" s="4">
         <v>8.0</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="4">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
@@ -471,7 +483,9 @@
       <c r="C8" s="4">
         <v>11.0</v>
       </c>
-      <c r="D8" s="5"/>
+      <c r="D8" s="4">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
@@ -483,7 +497,9 @@
       <c r="C9" s="4">
         <v>9.0</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9" s="4">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
@@ -495,7 +511,9 @@
       <c r="C10" s="4">
         <v>5.0</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="4">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
@@ -507,7 +525,9 @@
       <c r="C11" s="4">
         <v>2.0</v>
       </c>
-      <c r="D11" s="5"/>
+      <c r="D11" s="4">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
@@ -519,7 +539,9 @@
       <c r="C12" s="4">
         <v>1.0</v>
       </c>
-      <c r="D12" s="5"/>
+      <c r="D12" s="4">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
